--- a/internal_doc/05.测试设计/自动化/现有自动化用例更新策略.xlsx
+++ b/internal_doc/05.测试设计/自动化/现有自动化用例更新策略.xlsx
@@ -1105,11 +1105,11 @@
         <v>2</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="25.5" customHeight="1">
@@ -1121,11 +1121,11 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="25.5" customHeight="1">

--- a/internal_doc/05.测试设计/自动化/现有自动化用例更新策略.xlsx
+++ b/internal_doc/05.测试设计/自动化/现有自动化用例更新策略.xlsx
@@ -19,40 +19,239 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="61">
   <si>
     <t>aggregate</t>
   </si>
   <si>
+    <t>metaOperation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbLobTool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>split</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优先级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>次要责任人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例个数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特性名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例目录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aggregate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>procedures</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>backupRestore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbMigrate</t>
+  </si>
+  <si>
+    <t>transaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>邓强中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>余婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李春浩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>listCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>listCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collectionAlter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>delete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>truncate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upsert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>findandmodify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cursor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>countHint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>operators</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>selectorQuery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安排计划：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、每个特性由主要责任人负责更新筛选用例，由次要责任人负责检视。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、大家自行安排任务进度，计划3月11日之前完成上CI运行。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、更新或者删除的用例需要备注说明（如重复需要标记相同用例编号、无效用例需要简单描述原因），自动化用例路径如下：http://192.168.20.11/sequoiadb/trunk/testcases/hlt/js_testcases/js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>dataSync</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>metaOperation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdbLobTool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>split</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sql</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>优先级</t>
+    <t>syndate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -60,194 +259,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主要责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>次要责任人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基本操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例个数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特性名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例目录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aggregate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>procedures</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>backupRestore</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sdbMigrate</t>
-  </si>
-  <si>
-    <t>transaction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王文净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>邓强中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴艳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>余婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李春浩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>syndate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>listCS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropCS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>listCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>collectionAlter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lob</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>delete</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>truncate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upsert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>findandmodify</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>index</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropIndex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cursor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>countHint</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>operators</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>selectorQuery</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vote</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安排计划：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、每个特性由主要责任人负责更新筛选用例，由次要责任人负责检视。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、大家自行安排任务进度，计划3月11日之前完成上CI运行。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、更新或者删除的用例需要备注说明（如重复需要标记相同用例编号、无效用例需要简单描述原因），自动化用例路径如下：http://192.168.20.11/sequoiadb/trunk/testcases/hlt/js_testcases/js</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropCL</t>
+    <t>低</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -255,7 +267,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,6 +303,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -300,7 +320,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -347,11 +367,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -364,9 +393,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -741,25 +773,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>12</v>
-      </c>
       <c r="G1" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -767,600 +799,701 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1">
         <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="10">
+      <c r="A3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="11">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>24</v>
+      <c r="D3" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="33.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C4" s="5">
         <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1">
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1">
         <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1">
         <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C9" s="2">
         <v>21</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C11" s="1">
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="25.5" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C12" s="2">
         <v>22</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="25.5" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2">
         <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="25.5" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C14" s="2">
         <v>112</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="25.5" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C15" s="2">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="25.5" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2">
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="25.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="25.5" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2">
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="25.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="25.5" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2">
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="25.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="25.5" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2">
         <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="25.5" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="25.5" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C20" s="2">
         <v>39</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="25.5" customHeight="1">
+        <v>23</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="25.5" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2">
         <v>5</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="25.5" customHeight="1">
+        <v>26</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="25.5" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2">
         <v>2</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="25.5" customHeight="1">
+        <v>25</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="25.5" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="25.5" customHeight="1">
+        <v>25</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="25.5" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2">
         <v>25</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="25.5" customHeight="1">
+        <v>26</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="25.5" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2">
         <v>21</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1" t="s">
-        <v>52</v>
+        <v>26</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="25.5" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="C26" s="2">
         <v>6</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="27" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="G26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="27" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="2">
         <v>6</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="27" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="G27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="27" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1">
         <v>31</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="27" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="27" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1">
         <v>29</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>24</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="7">
         <v>23</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>26</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1">
         <v>36</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1">
         <v>17</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>13</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1">
         <v>12</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="29.25" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="29.25" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1">
         <v>17</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>27</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="7">
         <v>6</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>27</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="C36">
         <f>SUBTOTAL(9,C2:C35)</f>
         <v>582</v>
       </c>
       <c r="F36" s="1"/>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/自动化/现有自动化用例更新策略.xlsx
+++ b/internal_doc/05.测试设计/自动化/现有自动化用例更新策略.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="66">
   <si>
     <t>aggregate</t>
   </si>
@@ -260,6 +260,25 @@
   </si>
   <si>
     <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净</t>
+  </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -312,12 +331,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -380,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -399,80 +424,13 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -484,7 +442,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -761,7 +719,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
@@ -771,7 +730,7 @@
     <col min="5" max="5" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -794,7 +753,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8" hidden="1">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -817,7 +776,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="22.5" customHeight="1">
+    <row r="3" spans="1:8" ht="22.5" hidden="1" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>55</v>
       </c>
@@ -840,7 +799,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="33.75" customHeight="1">
+    <row r="4" spans="1:8" ht="33.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -859,11 +818,14 @@
       <c r="F4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="13.5" customHeight="1">
+      <c r="G4" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="13.5" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>29</v>
@@ -878,11 +840,14 @@
       <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="13.5" customHeight="1">
+      <c r="G5" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="13.5" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>30</v>
@@ -897,11 +862,14 @@
       <c r="F6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="13.5" customHeight="1">
+      <c r="G6" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="13.5" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>31</v>
@@ -916,11 +884,14 @@
       <c r="F7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="13.5" customHeight="1">
+      <c r="G7" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="13.5" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>32</v>
@@ -935,11 +906,14 @@
       <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="13.5" customHeight="1">
+      <c r="G8" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="13.5" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>34</v>
@@ -954,11 +928,14 @@
       <c r="F9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="13.5" customHeight="1">
+      <c r="G9" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="13.5" hidden="1" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
         <v>33</v>
@@ -973,11 +950,12 @@
       <c r="F10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="13.5" customHeight="1">
+      <c r="G10" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" ht="13.5" hidden="1" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
         <v>54</v>
@@ -992,11 +970,12 @@
       <c r="F11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G11" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" ht="25.5" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
@@ -1013,11 +992,14 @@
       <c r="F12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G12" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="25.5" hidden="1" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>36</v>
@@ -1032,11 +1014,12 @@
       <c r="F13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G13" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" ht="25.5" hidden="1" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
         <v>37</v>
@@ -1051,11 +1034,12 @@
       <c r="F14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G14" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" ht="25.5" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
         <v>38</v>
@@ -1070,11 +1054,14 @@
       <c r="F15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G15" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="25.5" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>39</v>
@@ -1089,11 +1076,14 @@
       <c r="F16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G16" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="25.5" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
         <v>40</v>
@@ -1108,11 +1098,14 @@
       <c r="F17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G17" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="25.5" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>41</v>
@@ -1127,11 +1120,14 @@
       <c r="F18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G18" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="25.5" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
         <v>42</v>
@@ -1146,11 +1142,14 @@
       <c r="F19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G19" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="25.5" hidden="1" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
         <v>43</v>
@@ -1165,11 +1164,14 @@
       <c r="F20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G20" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="25.5" hidden="1" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
         <v>44</v>
@@ -1184,11 +1186,14 @@
       <c r="F21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G21" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="25.5" hidden="1" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
         <v>45</v>
@@ -1203,11 +1208,14 @@
       <c r="F22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G22" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="25.5" hidden="1" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
         <v>46</v>
@@ -1222,11 +1230,14 @@
       <c r="F23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G23" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="25.5" hidden="1" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
         <v>47</v>
@@ -1241,11 +1252,14 @@
       <c r="F24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G24" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="25.5" hidden="1" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
         <v>48</v>
@@ -1260,11 +1274,14 @@
       <c r="F25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="25.5" customHeight="1">
+      <c r="G25" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="25.5" hidden="1" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>49</v>
       </c>
@@ -1281,8 +1298,11 @@
       <c r="G26" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="27" customHeight="1">
+      <c r="H26" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="27" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>18</v>
       </c>
@@ -1300,8 +1320,11 @@
       <c r="G27" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="27" customHeight="1">
+      <c r="H27" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="27" hidden="1" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>2</v>
       </c>
@@ -1318,11 +1341,14 @@
       <c r="F28" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="13" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="27" customHeight="1">
+      <c r="H28" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="27" hidden="1" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
@@ -1339,11 +1365,14 @@
       <c r="F29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="G29" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" hidden="1">
       <c r="A30" s="1" t="s">
         <v>6</v>
       </c>
@@ -1363,8 +1392,11 @@
       <c r="G30" s="13" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" hidden="1">
       <c r="A31" s="1" t="s">
         <v>5</v>
       </c>
@@ -1384,8 +1416,11 @@
       <c r="G31" s="13" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" hidden="1">
       <c r="A32" s="1" t="s">
         <v>21</v>
       </c>
@@ -1405,8 +1440,11 @@
       <c r="G32" s="13" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
         <v>20</v>
       </c>
@@ -1426,8 +1464,11 @@
       <c r="G33" s="13" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="29.25" customHeight="1">
+      <c r="H33" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="29.25" hidden="1" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>3</v>
       </c>
@@ -1447,8 +1488,11 @@
       <c r="G34" s="13" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" hidden="1">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -1468,36 +1512,46 @@
       <c r="G35" s="13" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="C36">
         <f>SUBTOTAL(9,C2:C35)</f>
-        <v>582</v>
+        <v>154</v>
       </c>
       <c r="F36" s="1"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F35">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="邓强中"/>
+        <filter val="李春浩"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
